--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
@@ -565,67 +565,67 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>12.454</v>
+        <v>12.3686</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2827</v>
+        <v>9.554500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1713</v>
+        <v>2.814</v>
       </c>
       <c r="G2" t="n">
-        <v>2.184</v>
+        <v>2.0956</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4814</v>
+        <v>3.4791</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.2974</v>
+        <v>-1.3836</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9427</v>
+        <v>5.0619</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6783</v>
+        <v>3.7897</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2645</v>
+        <v>1.2721</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7587</v>
+        <v>-2.9661</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1969</v>
+        <v>-0.3105000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.5618</v>
+        <v>-2.6558</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2775</v>
+        <v>-3.2393</v>
       </c>
       <c r="R2" t="n">
-        <v>5.7357</v>
+        <v>5.668699999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3466</v>
+        <v>4.301699999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2584</v>
+        <v>4.2834</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08810000000000001</v>
+        <v>0.01829999999999993</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4654</v>
+        <v>3.5418</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3592</v>
+        <v>3.4486</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9.731</v>
+        <v>9.6487</v>
       </c>
       <c r="E3" t="n">
-        <v>10.4826</v>
+        <v>10.6942</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7513000000000001</v>
+        <v>-1.045500000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0288</v>
+        <v>2.9878</v>
       </c>
       <c r="H3" t="n">
-        <v>6.244</v>
+        <v>6.2651</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.215100000000001</v>
+        <v>-3.2773</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1577</v>
+        <v>6.2828</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6044</v>
+        <v>5.7262</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5531999999999999</v>
+        <v>0.5566</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1287</v>
+        <v>-3.2951</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6395000000000001</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.7682</v>
+        <v>-3.8339</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R3" t="n">
-        <v>3.892</v>
+        <v>3.8467</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0876</v>
+        <v>3.0535</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6341</v>
+        <v>3.6468</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5466</v>
+        <v>-0.5934</v>
       </c>
       <c r="V3" t="n">
-        <v>1.771</v>
+        <v>1.7852</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7392</v>
+        <v>2.789</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9682999999999999</v>
+        <v>-1.0037</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.9572</v>
+        <v>7.9878</v>
       </c>
       <c r="E4" t="n">
-        <v>9.3546</v>
+        <v>9.806900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3972</v>
+        <v>-1.819</v>
       </c>
       <c r="G4" t="n">
-        <v>12.9102</v>
+        <v>12.9568</v>
       </c>
       <c r="H4" t="n">
-        <v>5.038600000000001</v>
+        <v>4.9842</v>
       </c>
       <c r="I4" t="n">
-        <v>7.871500000000001</v>
+        <v>7.972799999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>12.651</v>
+        <v>12.9454</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4731</v>
+        <v>1.5573</v>
       </c>
       <c r="L4" t="n">
-        <v>11.1779</v>
+        <v>11.3881</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2592</v>
+        <v>0.01139999999999985</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5656</v>
+        <v>3.4268</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.3062</v>
+        <v>-3.4154</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4581</v>
+        <v>2.4295</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.3017</v>
+        <v>-4.2516</v>
       </c>
       <c r="R4" t="n">
-        <v>6.7599</v>
+        <v>6.681</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.5044</v>
+        <v>-5.4554</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.5365</v>
+        <v>-2.4578</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.9679</v>
+        <v>-2.9977</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.9068</v>
+        <v>-1.943</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5418</v>
+        <v>3.5706</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.448600000000001</v>
+        <v>-5.5136</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8418</v>
+        <v>1.8824</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4558</v>
+        <v>3.1076</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6141000000000001</v>
+        <v>-1.2252</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3073</v>
+        <v>4.398</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9524</v>
+        <v>6.0441</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6451</v>
+        <v>-1.6463</v>
       </c>
       <c r="J5" t="n">
-        <v>7.7808</v>
+        <v>8.1898</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2341</v>
+        <v>6.509099999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5467</v>
+        <v>1.6807</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.4736</v>
+        <v>-3.7919</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2816000000000001</v>
+        <v>-0.465</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.1918</v>
+        <v>-3.3268</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q5" t="n">
-        <v>-10.4472</v>
+        <v>-10.3251</v>
       </c>
       <c r="R5" t="n">
-        <v>8.6036</v>
+        <v>8.503</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2849</v>
+        <v>1.2496</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0965</v>
+        <v>1.1703</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1884</v>
+        <v>0.07929999999999993</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9067</v>
+        <v>-1.9431</v>
       </c>
       <c r="W5" t="n">
-        <v>4.026</v>
+        <v>4.0724</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.932700000000001</v>
+        <v>-6.015499999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6814</v>
+        <v>1.5547</v>
       </c>
       <c r="E6" t="n">
-        <v>2.116</v>
+        <v>2.1999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4347000000000001</v>
+        <v>-0.6451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1501000000000001</v>
+        <v>0.0651999999999997</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0026</v>
+        <v>0.9514</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8524999999999999</v>
+        <v>-0.8862000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3257</v>
+        <v>1.3713</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0595</v>
+        <v>1.0859</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2661000000000001</v>
+        <v>0.2855</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1756</v>
+        <v>-1.3061</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.05690000000000007</v>
+        <v>-0.1344</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1186</v>
+        <v>-1.1717</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4824</v>
+        <v>3.4417</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1922</v>
+        <v>1.1896</v>
       </c>
       <c r="T6" t="n">
-        <v>2.511</v>
+        <v>2.5291</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3187</v>
+        <v>-1.3395</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1192</v>
+        <v>-2.1294</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1222000000000003</v>
+        <v>0.09400000000000031</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.7376</v>
+        <v>-3.4345</v>
       </c>
       <c r="F7" t="n">
-        <v>3.8598</v>
+        <v>3.528599999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3374</v>
+        <v>-1.3563</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8897999999999997</v>
+        <v>0.9271</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2272</v>
+        <v>-2.2834</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8258999999999996</v>
+        <v>0.9935</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2816</v>
+        <v>1.4164</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4557</v>
+        <v>-0.4228000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1632</v>
+        <v>-2.3498</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3917999999999999</v>
+        <v>-0.4892000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7716</v>
+        <v>-1.8605</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2534</v>
+        <v>2.2269</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R7" t="n">
-        <v>6.350199999999999</v>
+        <v>6.2761</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5813000000000001</v>
+        <v>-0.5901</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4963</v>
+        <v>-0.4435</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08510000000000001</v>
+        <v>-0.1466</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2124</v>
+        <v>-0.1864</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02969999999999995</v>
+        <v>0.0645</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="8">
@@ -1033,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0377</v>
+        <v>0.0345</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1687</v>
+        <v>0.1625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1060,31 +1060,31 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2507</v>
+        <v>-0.2473</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1197</v>
+        <v>-0.1192</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5133999999999994</v>
+        <v>-0.3489000000000004</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9386000000000003</v>
+        <v>1.574</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.452</v>
+        <v>-1.9229</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.573099999999999</v>
+        <v>-2.4864</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.861000000000001</v>
+        <v>-5.814</v>
       </c>
       <c r="I9" t="n">
-        <v>3.288</v>
+        <v>3.3275</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1579</v>
+        <v>3.5403</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.854800000000001</v>
+        <v>-4.6366</v>
       </c>
       <c r="L9" t="n">
-        <v>8.012700000000001</v>
+        <v>8.177</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.7309</v>
+        <v>-6.0267</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0061</v>
+        <v>-1.1774</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.724600000000001</v>
+        <v>-4.8495</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2048000000000001</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.3987</v>
+        <v>-8.300599999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>8.193899999999999</v>
+        <v>8.098100000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.2903</v>
+        <v>-3.2668</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3882</v>
+        <v>-1.309</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.902</v>
+        <v>-1.9578</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5548</v>
+        <v>5.606800000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>7.5678</v>
+        <v>7.643000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.013</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6591</v>
+        <v>-0.6576</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8278</v>
+        <v>-0.8202</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1687</v>
+        <v>0.1625</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6132</v>
+        <v>-0.6128</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4181</v>
+        <v>-0.4153</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2507</v>
+        <v>-0.2473</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1197</v>
+        <v>-0.1192</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6833</v>
+        <v>-1.6699</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.852</v>
+        <v>-1.8324</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1687</v>
+        <v>0.1625</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7526</v>
+        <v>-0.7512</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8919</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0558</v>
+        <v>-0.0591</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1113</v>
+        <v>-0.1089</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0196</v>
+        <v>0.0192</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8656</v>
+        <v>-1.958199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.3568</v>
+        <v>-4.986499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4913</v>
+        <v>3.0282</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5434</v>
+        <v>-3.6125</v>
       </c>
       <c r="H12" t="n">
-        <v>2.226</v>
+        <v>2.1581</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.769399999999999</v>
+        <v>-5.7706</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1098999999999997</v>
+        <v>0.3130999999999995</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6186</v>
+        <v>2.7038</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.508799999999999</v>
+        <v>-2.390599999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.6532</v>
+        <v>-3.9257</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3926</v>
+        <v>-0.5457000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.2605</v>
+        <v>-3.38</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4098000000000001</v>
+        <v>0.4048</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7.3745</v>
+        <v>-7.2883</v>
       </c>
       <c r="R12" t="n">
-        <v>7.7842</v>
+        <v>7.693199999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5716000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7273000000000001</v>
+        <v>0.7983000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1556</v>
+        <v>-0.2373</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6964</v>
+        <v>0.6884</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4842000000000001</v>
+        <v>-0.5017999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.1422</v>
+        <v>-13.996</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.8471</v>
+        <v>-14.4095</v>
       </c>
       <c r="F13" t="n">
-        <v>0.705</v>
+        <v>0.4136000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.6045</v>
+        <v>-6.519600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7776</v>
+        <v>-2.6925</v>
       </c>
       <c r="I13" t="n">
         <v>-3.8269</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.5189</v>
+        <v>-6.271</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.2534</v>
+        <v>-4.0808</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.2652</v>
+        <v>-2.1901</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08569999999999989</v>
+        <v>-0.2487</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4759</v>
+        <v>1.3882</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5615</v>
+        <v>-1.6369</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.3503</v>
+        <v>-6.276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2424</v>
+        <v>-10.1226</v>
       </c>
       <c r="R13" t="n">
-        <v>3.8921</v>
+        <v>3.8466</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7033</v>
+        <v>-0.6985</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2493</v>
+        <v>0.2919</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9527</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6647</v>
+        <v>1.6921</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1488</v>
+        <v>-2.1939</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>14.9617</v>
+        <v>14.9401</v>
       </c>
       <c r="E14" t="n">
-        <v>7.877999999999997</v>
+        <v>11.32590000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>7.084199999999999</v>
+        <v>3.614199999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>7.239800000000002</v>
+        <v>7.243899999999996</v>
       </c>
       <c r="H14" t="n">
-        <v>14.9139</v>
+        <v>15.018</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.674099999999998</v>
+        <v>-7.774100000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>29.03909999999999</v>
+        <v>31.04289999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>12.1446</v>
+        <v>13.3789</v>
       </c>
       <c r="L14" t="n">
-        <v>16.8946</v>
+        <v>17.6644</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.799</v>
+        <v>-23.7992</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7695</v>
+        <v>1.6391</v>
       </c>
       <c r="O14" t="n">
-        <v>-24.568</v>
+        <v>-25.4385</v>
       </c>
       <c r="P14" t="n">
-        <v>3.072800000000002</v>
+        <v>3.036700000000002</v>
       </c>
       <c r="Q14" t="n">
-        <v>-52.2358</v>
+        <v>-51.6257</v>
       </c>
       <c r="R14" t="n">
-        <v>55.30839999999999</v>
+        <v>54.6626</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2091000000000011</v>
+        <v>-0.2589</v>
       </c>
       <c r="T14" t="n">
-        <v>7.662599999999998</v>
+        <v>8.1252</v>
       </c>
       <c r="U14" t="n">
-        <v>-7.8719</v>
+        <v>-8.384300000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>4.8584</v>
+        <v>4.918400000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>23.4125</v>
+        <v>23.7821</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.5542</v>
+        <v>-18.8635</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3686</v>
+        <v>12.2041</v>
       </c>
       <c r="E2" t="n">
-        <v>9.554500000000001</v>
+        <v>12.4265</v>
       </c>
       <c r="F2" t="n">
-        <v>2.814</v>
+        <v>-0.2222999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0956</v>
+        <v>12.9568</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4791</v>
+        <v>4.9842</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.3836</v>
+        <v>7.972799999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0619</v>
+        <v>12.9454</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7897</v>
+        <v>1.5573</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2721</v>
+        <v>11.3881</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9661</v>
+        <v>0.01139999999999985</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3105000000000001</v>
+        <v>3.4268</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.6558</v>
+        <v>-3.4154</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4294</v>
+        <v>2.4295</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2393</v>
+        <v>-4.2516</v>
       </c>
       <c r="R2" t="n">
-        <v>5.668699999999999</v>
+        <v>6.681</v>
       </c>
       <c r="S2" t="n">
-        <v>4.301699999999999</v>
+        <v>-1.2392</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2834</v>
+        <v>0.1618999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01829999999999993</v>
+        <v>-1.401</v>
       </c>
       <c r="V2" t="n">
-        <v>3.5418</v>
+        <v>-1.943</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4486</v>
+        <v>3.5706</v>
       </c>
       <c r="X2" t="n">
-        <v>0.09320000000000001</v>
+        <v>-5.5136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>9.6487</v>
+        <v>9.744800000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>10.6942</v>
+        <v>7.0629</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.045500000000001</v>
+        <v>2.6818</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9878</v>
+        <v>2.0956</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2651</v>
+        <v>3.4791</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.2773</v>
+        <v>-1.3836</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2828</v>
+        <v>5.0619</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7262</v>
+        <v>3.7897</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5566</v>
+        <v>1.2721</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.2951</v>
+        <v>-2.9661</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5387999999999999</v>
+        <v>-0.3105000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.8339</v>
+        <v>-2.6558</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8221</v>
+        <v>2.4294</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0245</v>
+        <v>-3.2393</v>
       </c>
       <c r="R3" t="n">
-        <v>3.8467</v>
+        <v>5.668699999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0535</v>
+        <v>1.678</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6468</v>
+        <v>1.7918</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5934</v>
+        <v>-0.1138999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7852</v>
+        <v>3.5418</v>
       </c>
       <c r="W3" t="n">
-        <v>2.789</v>
+        <v>3.4486</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0037</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>7.9878</v>
+        <v>7.227300000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>9.806900000000001</v>
+        <v>8.3706</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.819</v>
+        <v>-1.1432</v>
       </c>
       <c r="G4" t="n">
-        <v>12.9568</v>
+        <v>2.9878</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9842</v>
+        <v>6.2651</v>
       </c>
       <c r="I4" t="n">
-        <v>7.972799999999999</v>
+        <v>-3.2773</v>
       </c>
       <c r="J4" t="n">
-        <v>12.9454</v>
+        <v>6.2828</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5573</v>
+        <v>5.7262</v>
       </c>
       <c r="L4" t="n">
-        <v>11.3881</v>
+        <v>0.5566</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01139999999999985</v>
+        <v>-3.2951</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4268</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.4154</v>
+        <v>-3.8339</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4295</v>
+        <v>1.8221</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.2516</v>
+        <v>-2.0245</v>
       </c>
       <c r="R4" t="n">
-        <v>6.681</v>
+        <v>3.8467</v>
       </c>
       <c r="S4" t="n">
-        <v>-5.4554</v>
+        <v>0.6321000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.4578</v>
+        <v>1.3231</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.9977</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.943</v>
+        <v>1.7852</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5706</v>
+        <v>2.789</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.5136</v>
+        <v>-1.0037</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8824</v>
+        <v>2.6159</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1076</v>
+        <v>3.5869</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2252</v>
+        <v>-0.9711000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>4.398</v>
@@ -844,13 +844,13 @@
         <v>8.503</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2496</v>
+        <v>1.9831</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1703</v>
+        <v>1.6495</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07929999999999993</v>
+        <v>0.3334999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-1.9431</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5547</v>
+        <v>2.5646</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1999</v>
+        <v>3.6745</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6451</v>
+        <v>-1.1099</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0651999999999997</v>
+        <v>-2.4864</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9514</v>
+        <v>-5.814</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8862000000000001</v>
+        <v>3.3275</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3713</v>
+        <v>3.5403</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0859</v>
+        <v>-4.6366</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2855</v>
+        <v>8.177</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3061</v>
+        <v>-6.0267</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1344</v>
+        <v>-1.1774</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1717</v>
+        <v>-4.8495</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4294</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0123</v>
+        <v>-8.300599999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4417</v>
+        <v>8.098100000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1896</v>
+        <v>-0.3533999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5291</v>
+        <v>0.7915999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.3395</v>
+        <v>-1.1448</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1294</v>
+        <v>5.606800000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6883</v>
+        <v>7.643000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4411</v>
+        <v>-2.0362</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09400000000000031</v>
+        <v>1.0979</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4345</v>
+        <v>-2.5002</v>
       </c>
       <c r="F7" t="n">
-        <v>3.528599999999999</v>
+        <v>3.598</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3563</v>
@@ -1000,13 +1000,13 @@
         <v>6.2761</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5901</v>
+        <v>0.4136</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4435</v>
+        <v>0.4906999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1466</v>
+        <v>-0.0771</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1864</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. TRIFONOV</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0345</v>
+        <v>0.7831000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1281</v>
+        <v>0.9785000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1625</v>
+        <v>-0.1954</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0793</v>
+        <v>0.0651999999999997</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1975</v>
+        <v>0.9514</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2768</v>
+        <v>-0.8862000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.3713</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.0859</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.2855</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0793</v>
+        <v>-1.3061</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1975</v>
+        <v>-0.1344</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2768</v>
+        <v>-1.1717</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2025</v>
+        <v>2.4294</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2025</v>
+        <v>3.4417</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2473</v>
+        <v>0.4179000000000002</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1281</v>
+        <v>1.3076</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1192</v>
+        <v>-0.8898</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.1294</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6883</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>T. TRIFONOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3489000000000004</v>
+        <v>0.0633</v>
       </c>
       <c r="E9" t="n">
-        <v>1.574</v>
+        <v>-0.1281</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9229</v>
+        <v>0.1913</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4864</v>
+        <v>0.0793</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.814</v>
+        <v>-0.1975</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3275</v>
+        <v>0.2768</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5403</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.6366</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8.177</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.0267</v>
+        <v>0.0793</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1774</v>
+        <v>-0.1975</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.8495</v>
+        <v>0.2768</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2025</v>
+        <v>0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.300599999999999</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>8.098100000000001</v>
+        <v>0.2025</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.2668</v>
+        <v>-0.2185</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.309</v>
+        <v>-0.1281</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.9578</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>5.606800000000001</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>7.643000000000001</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6576</v>
+        <v>-0.6288</v>
       </c>
       <c r="E10" t="n">
         <v>-0.8202</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1625</v>
+        <v>0.1913</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6128</v>
@@ -1234,13 +1234,13 @@
         <v>0.2025</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2473</v>
+        <v>-0.2185</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1281</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1192</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6699</v>
+        <v>-1.6411</v>
       </c>
       <c r="E11" t="n">
         <v>-1.8324</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1625</v>
+        <v>0.1913</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7512</v>
@@ -1312,13 +1312,13 @@
         <v>0.2025</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1089</v>
+        <v>-0.08</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1281</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0192</v>
+        <v>0.048</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.958199999999999</v>
+        <v>-1.9568</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.986499999999999</v>
+        <v>-5.1699</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0282</v>
+        <v>3.2129</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6125</v>
@@ -1390,13 +1390,13 @@
         <v>7.693199999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5624</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7983000000000002</v>
+        <v>0.6150000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2373</v>
+        <v>-0.0526</v>
       </c>
       <c r="V12" t="n">
         <v>0.6884</v>
@@ -1423,13 +1423,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.996</v>
+        <v>-12.341</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.4095</v>
+        <v>-13.6828</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4136000000000001</v>
+        <v>1.3418</v>
       </c>
       <c r="G13" t="n">
         <v>-6.519600000000001</v>
@@ -1468,13 +1468,13 @@
         <v>3.8466</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6985</v>
+        <v>0.9565</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2919</v>
+        <v>1.0185</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.06210000000000002</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5019</v>
@@ -1501,13 +1501,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>14.9401</v>
+        <v>19.7333</v>
       </c>
       <c r="E14" t="n">
-        <v>11.32590000000001</v>
+        <v>11.9663</v>
       </c>
       <c r="F14" t="n">
-        <v>3.614199999999999</v>
+        <v>7.7665</v>
       </c>
       <c r="G14" t="n">
         <v>7.243899999999996</v>
@@ -1546,13 +1546,13 @@
         <v>54.6626</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2589</v>
+        <v>4.534000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>8.1252</v>
+        <v>8.7654</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.384300000000001</v>
+        <v>-4.2316</v>
       </c>
       <c r="V14" t="n">
         <v>4.918400000000001</v>
